--- a/databases/tabela_resumo_clusters_ans_final1.xlsx
+++ b/databases/tabela_resumo_clusters_ans_final1.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,7 +418,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="D2">
         <v>3.9</v>
@@ -427,19 +427,19 @@
         <v>5.1</v>
       </c>
       <c r="F2">
-        <v>8.07</v>
+        <v>8.17</v>
       </c>
       <c r="G2">
         <v>7</v>
       </c>
       <c r="H2">
-        <v>4.14</v>
+        <v>5.55</v>
       </c>
       <c r="I2">
         <v>9.699999999999999</v>
       </c>
       <c r="J2">
-        <v>45.4</v>
+        <v>146.3</v>
       </c>
     </row>
     <row r="3">
@@ -476,39 +476,6 @@
       </c>
       <c r="J3">
         <v>3.8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ans_tx_abortos_mil_mulheres_valor_medio</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>146.3</v>
-      </c>
-      <c r="E4">
-        <v>146.3</v>
-      </c>
-      <c r="F4">
-        <v>146.3</v>
-      </c>
-      <c r="G4">
-        <v>146.3</v>
-      </c>
-      <c r="I4">
-        <v>146.3</v>
-      </c>
-      <c r="J4">
-        <v>146.3</v>
       </c>
     </row>
   </sheetData>
